--- a/markseet task.xlsx
+++ b/markseet task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel_task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6F48D61-277D-43D2-8F11-813B0F502EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152C27D4-3471-4B38-9642-D92CACE31887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{ED28128A-E1FF-4D56-9C72-61A05FB6AB73}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>eng</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Grade</t>
+  </si>
+  <si>
+    <t>SWITCH(M5</t>
   </si>
 </sst>
 </file>
@@ -434,14 +437,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE77E7DF-0C9F-4D86-959D-06C91AAF9950}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -479,7 +482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>9442</v>
       </c>
@@ -514,15 +517,18 @@
         <v>95.333333333333343</v>
       </c>
       <c r="K2" t="str">
-        <f>IF(AND(B2&gt;=35,C2&gt;=35,D2&gt;=35,E2&gt;=35,F2&gt;=35,G2&gt;=35),"pass","fail")</f>
+        <f>IF(AND(B2&gt;35,C2&gt;35,D2&gt;35,E2&gt;35,F2&gt;35,G2&gt;35),"pass","fail")</f>
         <v>pass</v>
       </c>
       <c r="L2" t="str">
-        <f>IF(J2&gt;=90,"A+",IF(J2&gt;=75,"A",IF(J2&gt;=55,"B",IF(J2&gt;=35,"C","D"))))</f>
+        <f>IF(J2&gt;=90,"A+",IF(J2&gt;=75,"A",IF(J2&gt;=65,"B",IF(J2&gt;=55,"C","D"))))</f>
         <v>A+</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>4883</v>
       </c>
@@ -552,20 +558,20 @@
         <f t="shared" ref="I3:I21" si="1">AVERAGE(B3:G3)</f>
         <v>56.333333333333336</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J21" si="2">H3/600*100</f>
         <v>56.333333333333336</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" ref="K3:K21" si="3">IF(AND(B3&gt;=35,C3&gt;=35,D3&gt;=35,E3&gt;=35,F3&gt;=35,G3&gt;=35),"pass","fail")</f>
+        <f t="shared" ref="K3:K21" si="3">IF(AND(B3&gt;35,C3&gt;35,D3&gt;35,E3&gt;35,F3&gt;35,G3&gt;35),"pass","fail")</f>
         <v>pass</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L21" si="4">IF(J3&gt;=90,"A+",IF(J3&gt;=75,"A",IF(J3&gt;=55,"B",IF(J3&gt;=35,"C","D"))))</f>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="L3:L21" si="4">IF(J3&gt;=90,"A+",IF(J3&gt;=75,"A",IF(J3&gt;=65,"B",IF(J3&gt;=55,"C","D"))))</f>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5098</v>
       </c>
@@ -605,10 +611,10 @@
       </c>
       <c r="L4" t="str">
         <f t="shared" si="4"/>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>6043</v>
       </c>
@@ -651,7 +657,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7341</v>
       </c>
@@ -694,7 +700,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7260</v>
       </c>
@@ -737,7 +743,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7441</v>
       </c>
@@ -777,10 +783,10 @@
       </c>
       <c r="L8" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7661</v>
       </c>
@@ -823,7 +829,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7442</v>
       </c>
@@ -834,28 +840,28 @@
         <v>92</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="E10">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="G10">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H10">
         <f t="shared" si="0"/>
-        <v>374</v>
+        <v>545</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
-        <v>62.333333333333336</v>
+        <v>90.833333333333329</v>
       </c>
       <c r="J10" s="2">
         <f t="shared" si="2"/>
-        <v>62.333333333333329</v>
+        <v>90.833333333333329</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="3"/>
@@ -863,10 +869,10 @@
       </c>
       <c r="L10" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>3157</v>
       </c>
@@ -906,10 +912,10 @@
       </c>
       <c r="L11" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2986</v>
       </c>
@@ -949,10 +955,10 @@
       </c>
       <c r="L12" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3024</v>
       </c>
@@ -992,10 +998,10 @@
       </c>
       <c r="L13" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>5332</v>
       </c>
@@ -1035,10 +1041,10 @@
       </c>
       <c r="L14" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>4548</v>
       </c>
@@ -1078,10 +1084,10 @@
       </c>
       <c r="L15" t="str">
         <f t="shared" si="4"/>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>9855</v>
       </c>
@@ -1121,7 +1127,7 @@
       </c>
       <c r="L16" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -1164,7 +1170,7 @@
       </c>
       <c r="L17" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -1207,7 +1213,7 @@
       </c>
       <c r="L18" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -1250,7 +1256,7 @@
       </c>
       <c r="L19" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
@@ -1293,7 +1299,7 @@
       </c>
       <c r="L20" t="str">
         <f t="shared" si="4"/>
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
@@ -1341,8 +1347,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="H2:H3 I3" formulaRange="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>